--- a/REPO DE IMAGENES.xlsx
+++ b/REPO DE IMAGENES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Dove\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53671D25-25ED-4873-AAFE-DF97AC2163CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287DBD11-C388-4AD9-8F8D-835EE6D850C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9CD91644-91B5-407B-9E9A-B1DB7EDBC739}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{9CD91644-91B5-407B-9E9A-B1DB7EDBC739}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="89">
   <si>
     <t>Dove Missions.jpeg</t>
   </si>
@@ -207,13 +207,114 @@
   </si>
   <si>
     <t>URL DE WIX</t>
+  </si>
+  <si>
+    <t>Liz Rooney</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/d88784_7778844f33de4d758ffc6716870f8c2d~mv2.jpg/v1/crop/x_404,y_1378,w_2731,h_3400/fill/w_211,h_264,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Liz_4.jpg</t>
+  </si>
+  <si>
+    <t>Vicky Mowl</t>
+  </si>
+  <si>
+    <t>executivedirector@doveyouthdevelopment.org &lt;executivedirector@doveyouthdevelopment.org&gt;</t>
+  </si>
+  <si>
+    <t>vicky@doveyouthdevelopment.org &lt;vicky@doveyouthdevelopment.org&gt;</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/d88784_fefa40778622481d82e420287f0b1173~mv2.jpg/v1/crop/x_491,y_1766,w_2642,h_3291/fill/w_211,h_263,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Vicky_18.jpg</t>
+  </si>
+  <si>
+    <t>Stina
+Johansson</t>
+  </si>
+  <si>
+    <t>stina@doveyouthdevelopment.org &lt;stina@doveyouthdevelopment.org&gt;</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_ce727aa643b7466ba01e604d03fd1d5d~mv2.jpeg/v1/fill/w_211,h_263,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/294108_ce727aa643b7466ba01e604d03fd1d5d~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>Régis Buzenet</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/d88784_5c09e4a410184483ab9f1b957e17c19c~mv2.jpg/v1/crop/x_468,y_2044,w_2602,h_3241/fill/w_211,h_263,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Regis_6.jpg</t>
+  </si>
+  <si>
+    <t>Teresa
+Cabrera Bonilla</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/d88784_03de129422654c18b2f0f178fbc9ea05~mv2.jpg/v1/crop/x_294,y_987,w_3114,h_3876/fill/w_211,h_264,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Teresa_10.jpg</t>
+  </si>
+  <si>
+    <t>Némesis Sánchez</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/d88784_2fd5cd4b7b614f9a8b6aa9897cb64bad~mv2.jpg/v1/crop/x_534,y_1981,w_2528,h_3149/fill/w_211,h_264,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Nemesis_3.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_57e242194dce4044b589a7295c6aa217~mv2.jpeg/v1/fill/w_211,h_264,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/294108_57e242194dce4044b589a7295c6aa217~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>Leonela Pena</t>
+  </si>
+  <si>
+    <t>Gustavo Reynoso</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/0d11bb_af6a5328e5e9490b8c546f58ce8246a0~mv2.jpg/v1/fill/w_206,h_264,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Gustavo%20_edited_edited.jpg</t>
+  </si>
+  <si>
+    <t>Amy Burkhalter</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/911777_e5551c17017d457e87d933fe8101d670~mv2.jpg/v1/crop/x_20,y_0,w_161,h_200/fill/w_173,h_215,al_c,lg_1,q_80,enc_avif,quality_auto/amy%2Bburkhalter.jpg</t>
+  </si>
+  <si>
+    <t>Deb Srbich</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_45aeab9bdd2d43a882751ed6fcb860d9~mv2.png/v1/fill/w_218,h_215,al_c,q_85,usm_0.66_1.00_0.01,enc_avif,quality_auto/294108_45aeab9bdd2d43a882751ed6fcb860d9~mv2.png</t>
+  </si>
+  <si>
+    <t>Dawn Kane</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_fc2b8529a0474f09b0d950e8182c7e8f~mv2.jpg/v1/fill/w_208,h_215,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/2025%20Dawn%20Kane.jpg</t>
+  </si>
+  <si>
+    <t>Edward Davison-Gwynn</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_0fe67c89d8264997b655fbacb6c3f6bf~mv2.jpg/v1/fill/w_218,h_221,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/ed%2Bgwynn_edited_edited.jpg</t>
+  </si>
+  <si>
+    <t>Caroline Gould</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_4769df6e7c7d4c0cba44f4e33ceb8ce0~mv2.png/v1/crop/x_0,y_69,w_147,h_183/fill/w_173,h_215,al_c,lg_1,q_85,enc_avif,quality_auto/image1.png</t>
+  </si>
+  <si>
+    <t>Cinzia Vittorio</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/294108_d5769c008bc24684a6d3a27b598389c3~mv2.png/v1/crop/x_0,y_69,w_147,h_183/fill/w_173,h_215,al_c,lg_1,q_85,enc_avif,quality_auto/image3.png</t>
+  </si>
+  <si>
+    <t>Lauren Belardinelli</t>
+  </si>
+  <si>
+    <t>Erika Camps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +329,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0AA399"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0AA399"/>
+      <name val="Algerian"/>
+      <family val="5"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,9 +364,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -589,359 +715,493 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05456F6-E2A7-4188-A5A5-CD62B92D401D}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="1" max="2" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>38</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{589FDA3C-313A-4677-A08C-44522839ECC2}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{DDE291D7-827C-42E4-8CBE-221E6A1AAABF}"/>
-    <hyperlink ref="B6" r:id="rId3" xr:uid="{22A6408D-804F-49FD-B818-3D0D6C7D7F08}"/>
-    <hyperlink ref="B8" r:id="rId4" xr:uid="{9CCA9D23-6C8A-4D79-859E-0838EB34BE18}"/>
-    <hyperlink ref="B9" r:id="rId5" xr:uid="{A32EF491-C8ED-46F0-8BAB-EFD7A7AA736E}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{7C23C97A-E198-44EA-AFEE-7E1414A221D2}"/>
-    <hyperlink ref="B38" r:id="rId7" xr:uid="{2538B7C2-85AD-461E-91DA-9922D641C636}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{589FDA3C-313A-4677-A08C-44522839ECC2}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{DDE291D7-827C-42E4-8CBE-221E6A1AAABF}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{22A6408D-804F-49FD-B818-3D0D6C7D7F08}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{9CCA9D23-6C8A-4D79-859E-0838EB34BE18}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{A32EF491-C8ED-46F0-8BAB-EFD7A7AA736E}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{7C23C97A-E198-44EA-AFEE-7E1414A221D2}"/>
+    <hyperlink ref="C38" r:id="rId7" xr:uid="{2538B7C2-85AD-461E-91DA-9922D641C636}"/>
+    <hyperlink ref="A43" r:id="rId8" display="mailto:executivedirector@doveyouthdevelopment.org" xr:uid="{B674B7F4-C431-4547-8094-74D4BFC5773D}"/>
+    <hyperlink ref="A44" r:id="rId9" display="mailto:vicky@doveyouthdevelopment.org" xr:uid="{5ABF5895-75FF-4A69-8293-BC67EEA8C2BB}"/>
+    <hyperlink ref="C49" r:id="rId10" xr:uid="{814934B6-C84D-464F-B442-676F9A8EAADD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>